--- a/Nhom01/SE_9/SE_9_Nhom01_NFR.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_NFR.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Each row has ID, description, source, type and note; there are at least 5 requirements.</t>
+          <t>Mỗi dòng có mã NFR, mô tả, nguồn, loại và ghi chú; có ít nhất 5 yêu cầu phi chức năng.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Rows 2–11, A:E</t>
+          <t>NFR-001–NFR-010</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Where supported by sources, types include security, authorization, backup, performance, audit trail and legal compliance.</t>
+          <t>Khi nguồn có căn cứ, các loại yêu cầu gồm bảo mật, phân quyền, sao lưu, hiệu năng, nhật ký kiểm toán và tuân thủ pháp luật.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>NFR-001…010; RAW-010/012</t>
+          <t>NFR-001–NFR-010; RAW-010; RAW-012</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Speed or retention requirements say how a tester would check them.</t>
+          <t>Yêu cầu có nêu tốc độ hoặc thời hạn lưu giữ phải nói rõ cách người kiểm thử xác minh.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>NFR-005, row 6</t>
+          <t>NFR-005</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
